--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-organization.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="481">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -202,13 +202,209 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Organization.implicitRules</t>
+    <t>Organization.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Organization.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Organization.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Organization.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Organization.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Organization.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>Organization.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Organization.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Organization.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -219,9 +415,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>Organization.language</t>
@@ -304,38 +497,10 @@
     <t>Organization.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:shortName</t>
@@ -434,26 +599,7 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Organization.identifier.use</t>
@@ -500,9 +646,6 @@
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-organization-identifier-type</t>
@@ -688,9 +831,6 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>Used to categorize the organization.</t>
   </si>
   <si>
@@ -735,10 +875,6 @@
   </si>
   <si>
     <t>Organization.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -1678,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN79"/>
+  <dimension ref="A1:AN88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.859375" customWidth="true" bestFit="true"/>
@@ -1704,7 +1840,7 @@
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="70.046875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="108.3828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
@@ -2081,10 +2217,10 @@
         <v>35</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>61</v>
@@ -2095,9 +2231,7 @@
       <c r="M4" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>64</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>35</v>
@@ -2146,25 +2280,25 @@
         <v>35</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK4" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL4" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="AK4" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AL4" t="s" s="2">
-        <v>66</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>35</v>
@@ -2175,21 +2309,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>35</v>
@@ -2236,28 +2370,28 @@
         <v>35</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>75</v>
@@ -2266,19 +2400,19 @@
         <v>36</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>35</v>
@@ -2289,14 +2423,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2312,19 +2446,19 @@
         <v>35</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2374,7 +2508,7 @@
         <v>35</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>36</v>
@@ -2392,7 +2526,7 @@
         <v>35</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>35</v>
@@ -2403,21 +2537,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>35</v>
@@ -2426,19 +2560,19 @@
         <v>35</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2488,25 +2622,25 @@
         <v>35</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>35</v>
@@ -2517,21 +2651,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>35</v>
@@ -2540,19 +2674,19 @@
         <v>35</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2590,37 +2724,37 @@
         <v>35</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>35</v>
@@ -2631,14 +2765,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>35</v>
       </c>
@@ -2647,7 +2779,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>35</v>
@@ -2656,18 +2788,20 @@
         <v>35</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>98</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>35</v>
@@ -2704,19 +2838,19 @@
         <v>35</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -2728,13 +2862,13 @@
         <v>57</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>35</v>
@@ -2745,13 +2879,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>35</v>
@@ -2770,18 +2904,20 @@
         <v>35</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>98</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>35</v>
@@ -2791,7 +2927,7 @@
         <v>35</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>35</v>
@@ -2830,7 +2966,7 @@
         <v>35</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -2842,13 +2978,13 @@
         <v>57</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>35</v>
@@ -2859,14 +2995,12 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>35</v>
       </c>
@@ -2875,7 +3009,7 @@
         <v>36</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>35</v>
@@ -2884,18 +3018,20 @@
         <v>35</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>35</v>
@@ -2920,13 +3056,13 @@
         <v>35</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>35</v>
@@ -2944,7 +3080,7 @@
         <v>35</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>36</v>
@@ -2956,13 +3092,13 @@
         <v>57</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>35</v>
@@ -2973,14 +3109,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2993,26 +3129,24 @@
         <v>35</v>
       </c>
       <c r="I12" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="J12" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>35</v>
       </c>
@@ -3036,31 +3170,31 @@
         <v>35</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
@@ -3072,13 +3206,13 @@
         <v>57</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>35</v>
@@ -3089,10 +3223,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3103,30 +3237,30 @@
         <v>36</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>46</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
         <v>125</v>
       </c>
+      <c r="N13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>35</v>
       </c>
@@ -3174,39 +3308,39 @@
         <v>35</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>130</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3229,15 +3363,17 @@
         <v>35</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>35</v>
@@ -3262,13 +3398,13 @@
         <v>35</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>35</v>
@@ -3286,7 +3422,7 @@
         <v>35</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>36</v>
@@ -3295,16 +3431,16 @@
         <v>45</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>35</v>
@@ -3315,21 +3451,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>35</v>
@@ -3341,16 +3477,16 @@
         <v>35</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3388,37 +3524,37 @@
         <v>35</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>35</v>
@@ -3429,46 +3565,44 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>35</v>
       </c>
@@ -3492,11 +3626,13 @@
         <v>35</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>35</v>
@@ -3514,25 +3650,25 @@
         <v>35</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>35</v>
@@ -3543,21 +3679,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>35</v>
@@ -3566,23 +3702,21 @@
         <v>35</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>35</v>
       </c>
@@ -3606,47 +3740,49 @@
         <v>35</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Y17" s="2"/>
-      <c r="Z17" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>156</v>
-      </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>35</v>
@@ -3657,18 +3793,20 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>45</v>
@@ -3680,23 +3818,19 @@
         <v>35</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>35</v>
       </c>
@@ -3708,7 +3842,7 @@
         <v>35</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>163</v>
+        <v>35</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>35</v>
@@ -3744,28 +3878,28 @@
         <v>35</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>165</v>
+        <v>35</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>167</v>
+        <v>35</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>35</v>
@@ -3773,18 +3907,20 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>45</v>
@@ -3796,20 +3932,18 @@
         <v>35</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>35</v>
@@ -3822,7 +3956,7 @@
         <v>35</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>172</v>
+        <v>35</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>35</v>
@@ -3858,28 +3992,28 @@
         <v>35</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>174</v>
+        <v>35</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>175</v>
+        <v>35</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>176</v>
+        <v>35</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>35</v>
@@ -3887,12 +4021,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>35</v>
       </c>
@@ -3910,20 +4046,18 @@
         <v>35</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>35</v>
@@ -3972,28 +4106,28 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>183</v>
+        <v>76</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>184</v>
+        <v>35</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>35</v>
@@ -4001,44 +4135,46 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>35</v>
       </c>
@@ -4074,40 +4210,40 @@
         <v>35</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>195</v>
+        <v>59</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>35</v>
@@ -4115,10 +4251,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4129,38 +4265,34 @@
         <v>36</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>46</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q22" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
         <v>35</v>
       </c>
@@ -4204,39 +4336,39 @@
         <v>35</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4247,7 +4379,7 @@
         <v>36</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>35</v>
@@ -4256,23 +4388,19 @@
         <v>35</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>35</v>
       </c>
@@ -4296,74 +4424,74 @@
         <v>35</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>214</v>
+        <v>35</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>215</v>
+        <v>35</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>208</v>
+        <v>64</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>218</v>
+        <v>65</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>219</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>35</v>
@@ -4372,23 +4500,21 @@
         <v>35</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>209</v>
+        <v>69</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>35</v>
       </c>
@@ -4412,29 +4538,31 @@
         <v>35</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>208</v>
+        <v>75</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -4446,27 +4574,27 @@
         <v>57</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>218</v>
+        <v>59</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>219</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4483,22 +4611,26 @@
         <v>35</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>35</v>
       </c>
@@ -4522,13 +4654,11 @@
         <v>35</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>35</v>
@@ -4546,7 +4676,7 @@
         <v>35</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
@@ -4555,16 +4685,16 @@
         <v>45</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>35</v>
@@ -4575,21 +4705,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>35</v>
@@ -4598,21 +4728,23 @@
         <v>35</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>35</v>
       </c>
@@ -4636,49 +4768,47 @@
         <v>35</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>35</v>
@@ -4689,10 +4819,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4715,19 +4845,19 @@
         <v>46</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>229</v>
+        <v>89</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>35</v>
@@ -4740,7 +4870,7 @@
         <v>35</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>35</v>
@@ -4776,13 +4906,13 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>57</v>
@@ -4791,13 +4921,13 @@
         <v>58</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>35</v>
@@ -4805,10 +4935,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4816,7 +4946,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>45</v>
@@ -4828,18 +4958,20 @@
         <v>35</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>35</v>
@@ -4852,7 +4984,7 @@
         <v>35</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>35</v>
+        <v>218</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>35</v>
@@ -4888,7 +5020,7 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -4897,19 +5029,19 @@
         <v>45</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>66</v>
+        <v>221</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>35</v>
@@ -4917,21 +5049,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>35</v>
@@ -4940,19 +5072,19 @@
         <v>35</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>93</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>94</v>
+        <v>225</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>96</v>
+        <v>227</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4990,40 +5122,40 @@
         <v>35</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>138</v>
+        <v>228</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>35</v>
@@ -5031,10 +5163,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5042,7 +5174,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>45</v>
@@ -5057,32 +5189,30 @@
         <v>46</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>61</v>
+        <v>234</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>35</v>
@@ -5118,7 +5248,7 @@
         <v>35</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5130,16 +5260,16 @@
         <v>57</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>58</v>
+        <v>239</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>35</v>
+        <v>242</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>35</v>
@@ -5147,10 +5277,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5167,28 +5297,32 @@
         <v>35</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>46</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q31" s="2"/>
+      <c r="Q31" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="R31" t="s" s="2">
         <v>35</v>
       </c>
@@ -5232,7 +5366,7 @@
         <v>35</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -5247,24 +5381,24 @@
         <v>58</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>35</v>
+        <v>252</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>35</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5275,7 +5409,7 @@
         <v>36</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>35</v>
@@ -5287,19 +5421,19 @@
         <v>46</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>35</v>
@@ -5324,37 +5458,35 @@
         <v>35</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>35</v>
+        <v>260</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>57</v>
@@ -5363,26 +5495,28 @@
         <v>58</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>35</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>35</v>
       </c>
@@ -5403,19 +5537,19 @@
         <v>46</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>35</v>
@@ -5440,13 +5574,11 @@
         <v>35</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>35</v>
+        <v>267</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>35</v>
@@ -5464,13 +5596,13 @@
         <v>35</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>57</v>
@@ -5479,24 +5611,24 @@
         <v>58</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>35</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5516,23 +5648,19 @@
         <v>35</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>198</v>
+        <v>61</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>278</v>
+        <v>62</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>35</v>
       </c>
@@ -5580,7 +5708,7 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>282</v>
+        <v>64</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -5589,16 +5717,16 @@
         <v>45</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>283</v>
+        <v>35</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>284</v>
+        <v>65</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>35</v>
@@ -5609,21 +5737,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>35</v>
@@ -5632,23 +5760,21 @@
         <v>35</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>287</v>
+        <v>69</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>35</v>
       </c>
@@ -5684,37 +5810,37 @@
         <v>35</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>292</v>
+        <v>35</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>293</v>
+        <v>59</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>35</v>
@@ -5725,20 +5851,18 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>45</v>
@@ -5753,19 +5877,19 @@
         <v>46</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>211</v>
+        <v>276</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>35</v>
@@ -5790,13 +5914,13 @@
         <v>35</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>296</v>
+        <v>35</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>297</v>
+        <v>35</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>35</v>
@@ -5814,7 +5938,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -5829,24 +5953,24 @@
         <v>58</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>219</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5869,13 +5993,13 @@
         <v>35</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5926,7 +6050,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -5944,7 +6068,7 @@
         <v>35</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>35</v>
@@ -5955,14 +6079,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>226</v>
+        <v>284</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5981,16 +6105,16 @@
         <v>35</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6028,19 +6152,19 @@
         <v>35</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -6052,7 +6176,7 @@
         <v>57</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>35</v>
@@ -6069,10 +6193,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>228</v>
+        <v>286</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6095,32 +6219,32 @@
         <v>46</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>229</v>
+        <v>89</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>35</v>
@@ -6156,13 +6280,13 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>57</v>
@@ -6171,10 +6295,10 @@
         <v>58</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>235</v>
+        <v>293</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>35</v>
@@ -6185,10 +6309,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6208,18 +6332,20 @@
         <v>35</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>35</v>
@@ -6268,7 +6394,7 @@
         <v>35</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
@@ -6277,16 +6403,16 @@
         <v>45</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>35</v>
+        <v>301</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>66</v>
+        <v>302</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>35</v>
@@ -6297,21 +6423,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>35</v>
@@ -6320,21 +6446,23 @@
         <v>35</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>94</v>
+        <v>305</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>35</v>
       </c>
@@ -6370,37 +6498,37 @@
         <v>35</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>138</v>
+        <v>309</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>59</v>
+        <v>311</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>35</v>
@@ -6411,10 +6539,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6422,7 +6550,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>45</v>
@@ -6440,29 +6568,29 @@
         <v>61</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>246</v>
+        <v>316</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>35</v>
@@ -6498,7 +6626,7 @@
         <v>35</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -6513,10 +6641,10 @@
         <v>58</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>35</v>
@@ -6527,10 +6655,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>252</v>
+        <v>321</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6553,18 +6681,20 @@
         <v>46</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>253</v>
+        <v>322</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>254</v>
+        <v>323</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>35</v>
       </c>
@@ -6612,7 +6742,7 @@
         <v>35</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>256</v>
+        <v>326</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -6627,10 +6757,10 @@
         <v>58</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>257</v>
+        <v>327</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>35</v>
@@ -6641,10 +6771,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6667,19 +6797,19 @@
         <v>46</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>261</v>
+        <v>331</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>35</v>
@@ -6728,7 +6858,7 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>265</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6743,10 +6873,10 @@
         <v>58</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>267</v>
+        <v>337</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>35</v>
@@ -6757,12 +6887,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>35</v>
       </c>
@@ -6783,19 +6915,19 @@
         <v>46</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>35</v>
@@ -6820,13 +6952,13 @@
         <v>35</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>35</v>
+        <v>340</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>35</v>
+        <v>341</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>35</v>
@@ -6844,13 +6976,13 @@
         <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>57</v>
@@ -6859,24 +6991,24 @@
         <v>58</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>35</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6896,23 +7028,19 @@
         <v>35</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>198</v>
+        <v>61</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>278</v>
+        <v>62</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>35</v>
       </c>
@@ -6960,7 +7088,7 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>282</v>
+        <v>64</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -6969,16 +7097,16 @@
         <v>45</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>283</v>
+        <v>35</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>284</v>
+        <v>65</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>35</v>
@@ -6989,21 +7117,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>35</v>
@@ -7012,23 +7140,21 @@
         <v>35</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>287</v>
+        <v>69</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>35</v>
       </c>
@@ -7064,37 +7190,37 @@
         <v>35</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>292</v>
+        <v>35</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>293</v>
+        <v>59</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>35</v>
@@ -7105,20 +7231,18 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>45</v>
@@ -7133,19 +7257,19 @@
         <v>46</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>211</v>
+        <v>276</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>35</v>
@@ -7170,13 +7294,13 @@
         <v>35</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>314</v>
+        <v>35</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>35</v>
@@ -7194,7 +7318,7 @@
         <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -7209,24 +7333,24 @@
         <v>58</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>219</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7249,13 +7373,13 @@
         <v>35</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7306,7 +7430,7 @@
         <v>35</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -7324,7 +7448,7 @@
         <v>35</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>35</v>
@@ -7335,14 +7459,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>284</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7361,16 +7485,16 @@
         <v>35</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7408,19 +7532,19 @@
         <v>35</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7432,7 +7556,7 @@
         <v>57</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>35</v>
@@ -7449,10 +7573,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>286</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7475,32 +7599,32 @@
         <v>46</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>89</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>230</v>
+        <v>348</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>231</v>
+        <v>348</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>35</v>
+        <v>349</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>35</v>
+        <v>349</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>35</v>
@@ -7536,13 +7660,13 @@
         <v>35</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>57</v>
@@ -7551,10 +7675,10 @@
         <v>58</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>235</v>
+        <v>293</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>35</v>
@@ -7565,10 +7689,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7588,18 +7712,20 @@
         <v>35</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>35</v>
@@ -7648,7 +7774,7 @@
         <v>35</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7657,16 +7783,16 @@
         <v>45</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>35</v>
+        <v>301</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>66</v>
+        <v>302</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>35</v>
@@ -7677,21 +7803,21 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>35</v>
@@ -7700,21 +7826,23 @@
         <v>35</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>94</v>
+        <v>305</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>35</v>
       </c>
@@ -7750,37 +7878,37 @@
         <v>35</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>138</v>
+        <v>309</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>59</v>
+        <v>311</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>35</v>
@@ -7791,10 +7919,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7802,7 +7930,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>45</v>
@@ -7820,23 +7948,23 @@
         <v>61</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>246</v>
+        <v>316</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>322</v>
+        <v>35</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>35</v>
@@ -7878,7 +8006,7 @@
         <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -7893,10 +8021,10 @@
         <v>58</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>35</v>
@@ -7907,10 +8035,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>252</v>
+        <v>321</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7933,18 +8061,20 @@
         <v>46</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>253</v>
+        <v>322</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>254</v>
+        <v>323</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>35</v>
       </c>
@@ -7992,7 +8122,7 @@
         <v>35</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>256</v>
+        <v>326</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -8007,10 +8137,10 @@
         <v>58</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>257</v>
+        <v>327</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>35</v>
@@ -8021,10 +8151,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8047,19 +8177,19 @@
         <v>46</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>261</v>
+        <v>331</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>35</v>
@@ -8108,7 +8238,7 @@
         <v>35</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>265</v>
+        <v>335</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
@@ -8123,10 +8253,10 @@
         <v>58</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>267</v>
+        <v>337</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>35</v>
@@ -8137,12 +8267,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>35</v>
       </c>
@@ -8163,19 +8295,19 @@
         <v>46</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>35</v>
@@ -8200,13 +8332,13 @@
         <v>35</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>35</v>
+        <v>357</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>35</v>
+        <v>358</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>35</v>
@@ -8224,13 +8356,13 @@
         <v>35</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>57</v>
@@ -8239,24 +8371,24 @@
         <v>58</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>35</v>
+        <v>264</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8276,23 +8408,19 @@
         <v>35</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>198</v>
+        <v>61</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>278</v>
+        <v>62</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>35</v>
       </c>
@@ -8340,7 +8468,7 @@
         <v>35</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>282</v>
+        <v>64</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
@@ -8349,16 +8477,16 @@
         <v>45</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>283</v>
+        <v>35</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>284</v>
+        <v>65</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>35</v>
@@ -8369,21 +8497,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>35</v>
@@ -8392,23 +8520,21 @@
         <v>35</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>287</v>
+        <v>69</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>288</v>
+        <v>70</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>35</v>
       </c>
@@ -8444,37 +8570,37 @@
         <v>35</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>292</v>
+        <v>35</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>293</v>
+        <v>59</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>35</v>
@@ -8485,10 +8611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>328</v>
+        <v>361</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8496,7 +8622,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>45</v>
@@ -8511,19 +8637,19 @@
         <v>46</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>329</v>
+        <v>274</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>330</v>
+        <v>275</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>331</v>
+        <v>276</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>332</v>
+        <v>277</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>35</v>
@@ -8572,28 +8698,28 @@
         <v>35</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>333</v>
+        <v>279</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>334</v>
+        <v>280</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>335</v>
+        <v>35</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>35</v>
@@ -8601,10 +8727,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>336</v>
+        <v>282</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8615,7 +8741,7 @@
         <v>36</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>35</v>
@@ -8627,20 +8753,16 @@
         <v>35</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>337</v>
+        <v>62</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>35</v>
       </c>
@@ -8688,25 +8810,25 @@
         <v>35</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>336</v>
+        <v>64</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>334</v>
+        <v>65</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>35</v>
@@ -8717,14 +8839,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>341</v>
+        <v>284</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8743,20 +8865,18 @@
         <v>35</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>342</v>
+        <v>68</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>343</v>
+        <v>69</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>344</v>
+        <v>70</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>35</v>
       </c>
@@ -8792,19 +8912,19 @@
         <v>35</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>341</v>
+        <v>75</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -8816,16 +8936,16 @@
         <v>57</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>347</v>
+        <v>76</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>348</v>
+        <v>35</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>349</v>
+        <v>59</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>35</v>
@@ -8833,10 +8953,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>351</v>
+        <v>286</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8844,10 +8964,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>35</v>
@@ -8856,29 +8976,29 @@
         <v>35</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>352</v>
+        <v>89</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>35</v>
+        <v>366</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>35</v>
@@ -8920,28 +9040,28 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>357</v>
+        <v>58</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>358</v>
+        <v>293</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>359</v>
+        <v>294</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>360</v>
+        <v>35</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>35</v>
@@ -8949,10 +9069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>361</v>
+        <v>296</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8975,20 +9095,18 @@
         <v>46</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>362</v>
+        <v>61</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>363</v>
+        <v>297</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>35</v>
       </c>
@@ -9036,7 +9154,7 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -9048,16 +9166,16 @@
         <v>57</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>193</v>
+        <v>58</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>204</v>
+        <v>301</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>367</v>
+        <v>302</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>35</v>
@@ -9068,7 +9186,7 @@
         <v>368</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9088,19 +9206,23 @@
         <v>35</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>133</v>
+        <v>305</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>35</v>
       </c>
@@ -9148,7 +9270,7 @@
         <v>35</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -9157,16 +9279,16 @@
         <v>45</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>66</v>
+        <v>311</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>35</v>
@@ -9180,18 +9302,18 @@
         <v>369</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>369</v>
+        <v>313</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>35</v>
@@ -9200,21 +9322,23 @@
         <v>35</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>94</v>
+        <v>314</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>137</v>
+        <v>315</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>35</v>
       </c>
@@ -9250,37 +9374,37 @@
         <v>35</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>138</v>
+        <v>317</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>35</v>
+        <v>318</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>59</v>
+        <v>319</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>35</v>
@@ -9294,7 +9418,7 @@
         <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9317,18 +9441,20 @@
         <v>46</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>371</v>
+        <v>322</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>35</v>
       </c>
@@ -9376,7 +9502,7 @@
         <v>35</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
@@ -9385,16 +9511,16 @@
         <v>45</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>375</v>
+        <v>57</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>35</v>
+        <v>327</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>59</v>
+        <v>328</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>35</v>
@@ -9405,10 +9531,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9434,15 +9560,17 @@
         <v>61</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>35</v>
       </c>
@@ -9466,11 +9594,13 @@
         <v>35</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>35</v>
@@ -9488,7 +9618,7 @@
         <v>35</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>380</v>
+        <v>335</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
@@ -9503,10 +9633,10 @@
         <v>58</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>35</v>
+        <v>336</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>59</v>
+        <v>337</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>35</v>
@@ -9517,10 +9647,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9543,18 +9673,20 @@
         <v>46</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>35</v>
       </c>
@@ -9602,7 +9734,7 @@
         <v>35</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -9611,19 +9743,19 @@
         <v>45</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>35</v>
@@ -9631,10 +9763,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9645,7 +9777,7 @@
         <v>36</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>35</v>
@@ -9654,21 +9786,23 @@
         <v>35</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>35</v>
       </c>
@@ -9716,13 +9850,13 @@
         <v>35</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>57</v>
@@ -9734,7 +9868,7 @@
         <v>35</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>59</v>
+        <v>378</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>35</v>
@@ -9745,10 +9879,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9771,19 +9905,19 @@
         <v>35</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>35</v>
@@ -9832,7 +9966,7 @@
         <v>35</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -9844,16 +9978,16 @@
         <v>57</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>58</v>
+        <v>391</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>35</v>
+        <v>392</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>35</v>
+        <v>394</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>35</v>
@@ -9861,10 +9995,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9875,7 +10009,7 @@
         <v>36</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>35</v>
@@ -9887,16 +10021,20 @@
         <v>35</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>132</v>
+        <v>396</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>133</v>
+        <v>397</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>35</v>
       </c>
@@ -9944,28 +10082,28 @@
         <v>35</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>135</v>
+        <v>395</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>35</v>
+        <v>401</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>35</v>
+        <v>402</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>66</v>
+        <v>403</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>35</v>
+        <v>404</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>35</v>
@@ -9973,21 +10111,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>35</v>
@@ -9996,21 +10134,23 @@
         <v>35</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>93</v>
+        <v>406</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>94</v>
+        <v>407</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>137</v>
+        <v>408</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>35</v>
       </c>
@@ -10046,40 +10186,40 @@
         <v>35</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>138</v>
+        <v>405</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>239</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>35</v>
+        <v>250</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>59</v>
+        <v>411</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>35</v>
@@ -10087,46 +10227,42 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>404</v>
+        <v>35</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>405</v>
+        <v>62</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>35</v>
       </c>
@@ -10174,25 +10310,25 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>407</v>
+        <v>64</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>35</v>
@@ -10203,21 +10339,21 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>35</v>
@@ -10229,20 +10365,18 @@
         <v>35</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>409</v>
+        <v>69</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>410</v>
+        <v>70</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>35</v>
       </c>
@@ -10266,49 +10400,49 @@
         <v>35</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>413</v>
+        <v>35</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>414</v>
+        <v>35</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>408</v>
+        <v>75</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>415</v>
+        <v>35</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>416</v>
+        <v>59</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>35</v>
@@ -10319,10 +10453,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10342,23 +10476,21 @@
         <v>35</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>418</v>
+        <v>61</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>35</v>
       </c>
@@ -10406,7 +10538,7 @@
         <v>35</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -10415,19 +10547,19 @@
         <v>45</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>57</v>
+        <v>419</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>423</v>
+        <v>35</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>424</v>
+        <v>59</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>425</v>
+        <v>35</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>35</v>
@@ -10435,10 +10567,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10449,7 +10581,7 @@
         <v>36</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>35</v>
@@ -10458,21 +10590,21 @@
         <v>35</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>342</v>
+        <v>89</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>343</v>
+        <v>421</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>35</v>
       </c>
@@ -10496,13 +10628,11 @@
         <v>35</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>35</v>
+        <v>267</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>35</v>
@@ -10520,28 +10650,28 @@
         <v>35</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>428</v>
+        <v>58</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>348</v>
+        <v>35</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>349</v>
+        <v>59</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>35</v>
@@ -10549,10 +10679,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10572,23 +10702,21 @@
         <v>35</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>352</v>
+        <v>175</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>353</v>
+        <v>426</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>354</v>
+        <v>427</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>35</v>
       </c>
@@ -10651,13 +10779,13 @@
         <v>58</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>358</v>
+        <v>430</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>359</v>
+        <v>431</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>35</v>
@@ -10665,10 +10793,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10679,7 +10807,7 @@
         <v>36</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>35</v>
@@ -10688,23 +10816,21 @@
         <v>35</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>432</v>
+        <v>61</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>35</v>
       </c>
@@ -10752,30 +10878,1066 @@
         <v>35</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>57</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>193</v>
+        <v>58</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>436</v>
+        <v>59</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AN79" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>35</v>
       </c>
     </row>
